--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="采购建议明细" sheetId="1" r:id="rId1"/>
+    <sheet name="单品集中采购" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
   <si>
     <t>类型</t>
   </si>
@@ -1283,4 +1284,48 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="15.75" customWidth="1"/>
+    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>类型</t>
   </si>
@@ -1289,15 +1289,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="15.75" customWidth="1"/>
-    <col min="5" max="5" width="15.125" customWidth="1"/>
-    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="16.625" customWidth="1"/>
     <col min="7" max="7" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1324,6 +1324,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="采购建议明细" sheetId="1" r:id="rId1"/>
-    <sheet name="单品集中采购" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>类型</t>
   </si>
@@ -90,12 +89,18 @@
     <t>预计采购成本（系统）</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>创建方式</t>
   </si>
   <si>
     <t>创建人</t>
   </si>
   <si>
+    <t>创建时间</t>
+  </si>
+  <si>
     <t>更新人</t>
   </si>
   <si>
@@ -162,10 +167,16 @@
     <t>{.sysPurchaseCost}</t>
   </si>
   <si>
-    <t>{.createTypeName}</t>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.dataTypeName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
   <si>
     <t>{.updateUserName}</t>
@@ -1102,7 +1113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -1125,13 +1136,13 @@
     <col min="18" max="18" width="19.875" customWidth="1"/>
     <col min="19" max="19" width="16.25" customWidth="1"/>
     <col min="20" max="20" width="19.125" customWidth="1"/>
-    <col min="21" max="21" width="16.375" customWidth="1"/>
-    <col min="22" max="22" width="17.125" customWidth="1"/>
-    <col min="23" max="23" width="15.375" customWidth="1"/>
-    <col min="24" max="24" width="15.125" customWidth="1"/>
+    <col min="21" max="22" width="16.375" customWidth="1"/>
+    <col min="23" max="23" width="17.125" customWidth="1"/>
+    <col min="24" max="25" width="15.375" customWidth="1"/>
+    <col min="26" max="26" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1204,79 +1215,91 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1284,71 +1307,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18.375" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="19.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>类型</t>
   </si>
@@ -59,6 +59,12 @@
     <t>采购备货数</t>
   </si>
   <si>
+    <t>是否下推</t>
+  </si>
+  <si>
+    <t>采购申请单号</t>
+  </si>
+  <si>
     <t>物流方式</t>
   </si>
   <si>
@@ -135,6 +141,12 @@
   </si>
   <si>
     <t>{.purchaseStockUpQty}</t>
+  </si>
+  <si>
+    <t>{.isPushName}</t>
+  </si>
+  <si>
+    <t>{.purchaseApplicationCode}</t>
   </si>
   <si>
     <t>{.logisticsMethodName}</t>
@@ -1113,7 +1125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -1125,24 +1137,25 @@
     <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="17.125" customWidth="1"/>
     <col min="9" max="9" width="19.125" customWidth="1"/>
-    <col min="10" max="10" width="14.75" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="18.25" customWidth="1"/>
-    <col min="13" max="13" width="19.5" customWidth="1"/>
-    <col min="14" max="14" width="21.125" customWidth="1"/>
-    <col min="15" max="15" width="18.375" customWidth="1"/>
-    <col min="16" max="16" width="19.375" customWidth="1"/>
-    <col min="17" max="17" width="18.25" customWidth="1"/>
-    <col min="18" max="18" width="19.875" customWidth="1"/>
-    <col min="19" max="19" width="16.25" customWidth="1"/>
-    <col min="20" max="20" width="19.125" customWidth="1"/>
-    <col min="21" max="22" width="16.375" customWidth="1"/>
-    <col min="23" max="23" width="17.125" customWidth="1"/>
-    <col min="24" max="25" width="15.375" customWidth="1"/>
-    <col min="26" max="26" width="15.125" customWidth="1"/>
+    <col min="10" max="11" width="14.75" customWidth="1"/>
+    <col min="12" max="12" width="21.625" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="18.25" customWidth="1"/>
+    <col min="15" max="15" width="19.5" customWidth="1"/>
+    <col min="16" max="16" width="21.125" customWidth="1"/>
+    <col min="17" max="17" width="18.375" customWidth="1"/>
+    <col min="18" max="18" width="19.375" customWidth="1"/>
+    <col min="19" max="19" width="18.25" customWidth="1"/>
+    <col min="20" max="20" width="19.875" customWidth="1"/>
+    <col min="21" max="21" width="16.25" customWidth="1"/>
+    <col min="22" max="22" width="19.125" customWidth="1"/>
+    <col min="23" max="24" width="16.375" customWidth="1"/>
+    <col min="25" max="25" width="17.125" customWidth="1"/>
+    <col min="26" max="27" width="15.375" customWidth="1"/>
+    <col min="28" max="28" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1221,85 +1234,97 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/purchaseSuggestionEntity.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>类型</t>
   </si>
@@ -65,12 +65,6 @@
     <t>采购申请单号</t>
   </si>
   <si>
-    <t>物流方式</t>
-  </si>
-  <si>
-    <t>物流方式（系统）</t>
-  </si>
-  <si>
     <t>建议采购日期</t>
   </si>
   <si>
@@ -147,12 +141,6 @@
   </si>
   <si>
     <t>{.purchaseApplicationCode}</t>
-  </si>
-  <si>
-    <t>{.logisticsMethodName}</t>
-  </si>
-  <si>
-    <t>{.sysLogisticsMethodName}</t>
   </si>
   <si>
     <t>{.suggestPurchaseDate}</t>
@@ -1125,7 +1113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -1139,23 +1127,21 @@
     <col min="9" max="9" width="19.125" customWidth="1"/>
     <col min="10" max="11" width="14.75" customWidth="1"/>
     <col min="12" max="12" width="21.625" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-    <col min="15" max="15" width="19.5" customWidth="1"/>
-    <col min="16" max="16" width="21.125" customWidth="1"/>
-    <col min="17" max="17" width="18.375" customWidth="1"/>
-    <col min="18" max="18" width="19.375" customWidth="1"/>
-    <col min="19" max="19" width="18.25" customWidth="1"/>
-    <col min="20" max="20" width="19.875" customWidth="1"/>
-    <col min="21" max="21" width="16.25" customWidth="1"/>
-    <col min="22" max="22" width="19.125" customWidth="1"/>
-    <col min="23" max="24" width="16.375" customWidth="1"/>
-    <col min="25" max="25" width="17.125" customWidth="1"/>
-    <col min="26" max="27" width="15.375" customWidth="1"/>
-    <col min="28" max="28" width="15.125" customWidth="1"/>
+    <col min="13" max="13" width="19.5" customWidth="1"/>
+    <col min="14" max="14" width="21.125" customWidth="1"/>
+    <col min="15" max="15" width="18.375" customWidth="1"/>
+    <col min="16" max="16" width="19.375" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="18" max="18" width="19.875" customWidth="1"/>
+    <col min="19" max="19" width="16.25" customWidth="1"/>
+    <col min="20" max="20" width="19.125" customWidth="1"/>
+    <col min="21" max="22" width="16.375" customWidth="1"/>
+    <col min="23" max="23" width="17.125" customWidth="1"/>
+    <col min="24" max="25" width="15.375" customWidth="1"/>
+    <col min="26" max="26" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1234,97 +1220,85 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>40</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>41</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>42</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>44</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>45</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>46</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>47</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>48</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>50</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>51</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
